--- a/consent_forms/040_child_support_agreement_form--consent_forms.xlsx
+++ b/consent_forms/040_child_support_agreement_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -985,8 +985,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'bi-weekly',_'value':_'biweekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Bi-weekly', 'value': 'biweekly'}</t>
+          <t>Bi-weekly</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'health_and_dental_insurance',_'value':_'insurance'}</t>
+          <t>health_and_dental_insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Health and Dental Insurance', 'value': 'insurance'}</t>
+          <t>Health and Dental Insurance</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'school_tuition_and_fees',_'value':_'education'}</t>
+          <t>school_tuition_and_fees</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'School Tuition and Fees', 'value': 'education'}</t>
+          <t>School Tuition and Fees</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'extracurricular_and_sports',_'value':_'sports'}</t>
+          <t>extracurricular_and_sports</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Extracurricular and Sports', 'value': 'sports'}</t>
+          <t>Extracurricular and Sports</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'childcare_and_daycare',_'value':_'childcare'}</t>
+          <t>childcare_and_daycare</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Childcare and Daycare', 'value': 'childcare'}</t>
+          <t>Childcare and Daycare</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'sole_custody_parent_a',_'value':_'sole_a'}</t>
+          <t>sole_custody_parent_a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Sole Custody Parent A', 'value': 'sole_a'}</t>
+          <t>Sole Custody Parent A</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'sole_custody_parent_b',_'value':_'sole_b'}</t>
+          <t>sole_custody_parent_b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Sole Custody Parent B', 'value': 'sole_b'}</t>
+          <t>Sole Custody Parent B</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'joint_physical_custody',_'value':_'joint'}</t>
+          <t>joint_physical_custody</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Joint Physical Custody', 'value': 'joint'}</t>
+          <t>Joint Physical Custody</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_we_agree',_'value':_true}</t>
+          <t>yes_-_we_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - We Agree', 'value': True}</t>
+          <t>Yes - We Agree</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_yet_agreed',_'value':_false}</t>
+          <t>no_-_not_yet_agreed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not yet agreed', 'value': False}</t>
+          <t>No - Not yet agreed</t>
         </is>
       </c>
     </row>
